--- a/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$type）.xlsx
+++ b/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$type）.xlsx
@@ -173,23 +173,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;:{$type:&lt;BSON type&gt;}}查询，目标字段覆盖所有数据类型，value取值覆盖所有数据类型编码
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$type:&lt;BSON type&gt;}}查询，目标字段覆盖所有数据类型，value取值覆盖所有数据类型编码；目标字段为索引字段
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$type:&lt;BSON type&gt;}}查询，value取无效编码
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、查询成功，返回与给定类型匹配的记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$type:&lt;BSON type&gt;}})查询，目标字段覆盖所有数据类型，value取值覆盖所有数据类型编码
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$type:&lt;BSON type&gt;}})查询，目标字段覆盖所有数据类型，value取值覆盖所有数据类型编码；目标字段为索引字段
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$type:&lt;BSON type&gt;}})查询，value取无效编码
+2、检查查询结果正确性</t>
   </si>
 </sst>
 </file>
@@ -268,31 +265,31 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
@@ -354,31 +351,31 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I4" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
   <autoFilter ref="A1:I4"/>
   <tableColumns count="9">
-    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="0">
+    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="8">
+    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="7">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/summary" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="7">
+    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/preconditions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="6">
+    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/execution_type" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="5">
+    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/importance" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="4">
+    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/step_number" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="3">
+    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="2">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/actions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="2">
+    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="1">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/expectedresults" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="1">
+    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="0">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/execution_type" xmlDataType="integer"/>
     </tableColumn>
   </tableColumns>
@@ -733,10 +730,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
@@ -759,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -786,10 +783,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
